--- a/data/1st Round/Corrected/CdS2_Results Table.xlsx
+++ b/data/1st Round/Corrected/CdS2_Results Table.xlsx
@@ -2,15 +2,14 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="1" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="3804" yWindow="2340" windowWidth="17280" windowHeight="8880" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="Corrected Results" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -50,7 +49,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -413,8 +412,8 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R29"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:T29"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.4"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
@@ -507,6 +506,16 @@
           <t>Date</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>Rseriescm2</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Rshuntcm2</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -547,9 +556,6 @@
       <c r="L2" t="n">
         <v>0.00028744</v>
       </c>
-      <c r="M2" t="inlineStr"/>
-      <c r="N2" t="inlineStr"/>
-      <c r="O2" t="inlineStr"/>
       <c r="P2" t="n">
         <v>19.248</v>
       </c>
@@ -563,6 +569,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S2" t="n">
+        <v>13.37460563909487</v>
+      </c>
+      <c r="T2" t="n">
+        <v>81.71178685427871</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -603,9 +615,6 @@
       <c r="L3" t="n">
         <v>0.0005607</v>
       </c>
-      <c r="M3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="O3" t="inlineStr"/>
       <c r="P3" t="n">
         <v>18.992</v>
       </c>
@@ -619,6 +628,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S3" t="n">
+        <v>11.62503022454319</v>
+      </c>
+      <c r="T3" t="n">
+        <v>52.18484887140538</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -659,9 +674,6 @@
       <c r="L4" t="n">
         <v>0.00042094</v>
       </c>
-      <c r="M4" t="inlineStr"/>
-      <c r="N4" t="inlineStr"/>
-      <c r="O4" t="inlineStr"/>
       <c r="P4" t="n">
         <v>18.993</v>
       </c>
@@ -675,6 +687,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S4" t="n">
+        <v>13.94425060085733</v>
+      </c>
+      <c r="T4" t="n">
+        <v>46.10473213480162</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -715,9 +733,6 @@
       <c r="L5" t="n">
         <v>0.00020486</v>
       </c>
-      <c r="M5" t="inlineStr"/>
-      <c r="N5" t="inlineStr"/>
-      <c r="O5" t="inlineStr"/>
       <c r="P5" t="n">
         <v>18.987</v>
       </c>
@@ -731,6 +746,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S5" t="n">
+        <v>15.90129217228153</v>
+      </c>
+      <c r="T5" t="n">
+        <v>30.13073962170873</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -771,9 +792,6 @@
       <c r="L6" t="n">
         <v>0.00031902</v>
       </c>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
       <c r="P6" t="n">
         <v>18.991</v>
       </c>
@@ -787,6 +805,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S6" t="n">
+        <v>12.29002573329954</v>
+      </c>
+      <c r="T6" t="n">
+        <v>95.22117783569838</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -827,9 +851,6 @@
       <c r="L7" t="n">
         <v>4.771e-05</v>
       </c>
-      <c r="M7" t="inlineStr"/>
-      <c r="N7" t="inlineStr"/>
-      <c r="O7" t="inlineStr"/>
       <c r="P7" t="n">
         <v>19.29</v>
       </c>
@@ -843,6 +864,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S7" t="n">
+        <v>9.280419539422581</v>
+      </c>
+      <c r="T7" t="n">
+        <v>10.41582310993411</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -883,9 +910,6 @@
       <c r="L8" t="n">
         <v>0.00019702</v>
       </c>
-      <c r="M8" t="inlineStr"/>
-      <c r="N8" t="inlineStr"/>
-      <c r="O8" t="inlineStr"/>
       <c r="P8" t="n">
         <v>18.978</v>
       </c>
@@ -899,6 +923,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S8" t="n">
+        <v>15.12476056503754</v>
+      </c>
+      <c r="T8" t="n">
+        <v>30.16183516793412</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -939,9 +969,6 @@
       <c r="L9" t="n">
         <v>0.00034438</v>
       </c>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
       <c r="P9" t="n">
         <v>18.967</v>
       </c>
@@ -955,6 +982,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S9" t="n">
+        <v>15.22057486751145</v>
+      </c>
+      <c r="T9" t="n">
+        <v>56.45672316037282</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -995,9 +1028,6 @@
       <c r="L10" t="n">
         <v>0.00042378</v>
       </c>
-      <c r="M10" t="inlineStr"/>
-      <c r="N10" t="inlineStr"/>
-      <c r="O10" t="inlineStr"/>
       <c r="P10" t="n">
         <v>18.985</v>
       </c>
@@ -1011,6 +1041,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S10" t="n">
+        <v>13.64924528971435</v>
+      </c>
+      <c r="T10" t="n">
+        <v>58.46183206247891</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1051,9 +1087,6 @@
       <c r="L11" t="n">
         <v>0.00028385</v>
       </c>
-      <c r="M11" t="inlineStr"/>
-      <c r="N11" t="inlineStr"/>
-      <c r="O11" t="inlineStr"/>
       <c r="P11" t="n">
         <v>18.987</v>
       </c>
@@ -1067,6 +1100,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S11" t="n">
+        <v>15.09108053792624</v>
+      </c>
+      <c r="T11" t="n">
+        <v>73.41062304249395</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1107,9 +1146,6 @@
       <c r="L12" t="n">
         <v>0.00041044</v>
       </c>
-      <c r="M12" t="inlineStr"/>
-      <c r="N12" t="inlineStr"/>
-      <c r="O12" t="inlineStr"/>
       <c r="P12" t="n">
         <v>18.992</v>
       </c>
@@ -1123,6 +1159,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S12" t="n">
+        <v>13.23240184363969</v>
+      </c>
+      <c r="T12" t="n">
+        <v>42.00694255455874</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1163,9 +1205,6 @@
       <c r="L13" t="n">
         <v>0.00040957</v>
       </c>
-      <c r="M13" t="inlineStr"/>
-      <c r="N13" t="inlineStr"/>
-      <c r="O13" t="inlineStr"/>
       <c r="P13" t="n">
         <v>18.993</v>
       </c>
@@ -1179,6 +1218,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S13" t="n">
+        <v>13.32635299289849</v>
+      </c>
+      <c r="T13" t="n">
+        <v>36.30439404236335</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1219,9 +1264,6 @@
       <c r="L14" t="n">
         <v>0.00036207</v>
       </c>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
       <c r="P14" t="n">
         <v>18.98</v>
       </c>
@@ -1235,6 +1277,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S14" t="n">
+        <v>15.2805708796201</v>
+      </c>
+      <c r="T14" t="n">
+        <v>55.31507428237229</v>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1275,9 +1323,6 @@
       <c r="L15" t="n">
         <v>0.00034035</v>
       </c>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
       <c r="P15" t="n">
         <v>19.244</v>
       </c>
@@ -1291,6 +1336,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S15" t="n">
+        <v>15.18006850642345</v>
+      </c>
+      <c r="T15" t="n">
+        <v>45.98477649308729</v>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1331,9 +1382,6 @@
       <c r="L16" t="n">
         <v>9.807e-05</v>
       </c>
-      <c r="M16" t="inlineStr"/>
-      <c r="N16" t="inlineStr"/>
-      <c r="O16" t="inlineStr"/>
       <c r="P16" t="n">
         <v>18.995</v>
       </c>
@@ -1347,6 +1395,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S16" t="n">
+        <v>15.10453412357968</v>
+      </c>
+      <c r="T16" t="n">
+        <v>18.71994191524921</v>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1387,9 +1441,6 @@
       <c r="L17" t="n">
         <v>9.014e-05</v>
       </c>
-      <c r="M17" t="inlineStr"/>
-      <c r="N17" t="inlineStr"/>
-      <c r="O17" t="inlineStr"/>
       <c r="P17" t="n">
         <v>19.242</v>
       </c>
@@ -1403,6 +1454,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S17" t="n">
+        <v>13.02497400680199</v>
+      </c>
+      <c r="T17" t="n">
+        <v>17.18906559685465</v>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1443,9 +1500,6 @@
       <c r="L18" t="n">
         <v>0.00023718</v>
       </c>
-      <c r="M18" t="inlineStr"/>
-      <c r="N18" t="inlineStr"/>
-      <c r="O18" t="inlineStr"/>
       <c r="P18" t="n">
         <v>18.987</v>
       </c>
@@ -1459,6 +1513,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S18" t="n">
+        <v>15.2469656834728</v>
+      </c>
+      <c r="T18" t="n">
+        <v>41.68618586459545</v>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1499,9 +1559,6 @@
       <c r="L19" t="n">
         <v>0.00022488</v>
       </c>
-      <c r="M19" t="inlineStr"/>
-      <c r="N19" t="inlineStr"/>
-      <c r="O19" t="inlineStr"/>
       <c r="P19" t="n">
         <v>19.258</v>
       </c>
@@ -1515,6 +1572,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S19" t="n">
+        <v>12.38185282095868</v>
+      </c>
+      <c r="T19" t="n">
+        <v>17.70422669071798</v>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1555,9 +1618,6 @@
       <c r="L20" t="n">
         <v>0.00030721</v>
       </c>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
       <c r="P20" t="n">
         <v>19.249</v>
       </c>
@@ -1571,6 +1631,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S20" t="n">
+        <v>14.22980078123329</v>
+      </c>
+      <c r="T20" t="n">
+        <v>31.44400099216774</v>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1611,9 +1677,6 @@
       <c r="L21" t="n">
         <v>0.00028606</v>
       </c>
-      <c r="M21" t="inlineStr"/>
-      <c r="N21" t="inlineStr"/>
-      <c r="O21" t="inlineStr"/>
       <c r="P21" t="n">
         <v>19.245</v>
       </c>
@@ -1627,6 +1690,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S21" t="n">
+        <v>12.36391415469481</v>
+      </c>
+      <c r="T21" t="n">
+        <v>49.19410286708446</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1667,9 +1736,6 @@
       <c r="L22" t="n">
         <v>0.00034758</v>
       </c>
-      <c r="M22" t="inlineStr"/>
-      <c r="N22" t="inlineStr"/>
-      <c r="O22" t="inlineStr"/>
       <c r="P22" t="n">
         <v>19.493</v>
       </c>
@@ -1683,6 +1749,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S22" t="n">
+        <v>11.34768353367828</v>
+      </c>
+      <c r="T22" t="n">
+        <v>17.60015315178036</v>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1723,9 +1795,6 @@
       <c r="L23" t="n">
         <v>0.00054026</v>
       </c>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
       <c r="P23" t="n">
         <v>18.992</v>
       </c>
@@ -1739,6 +1808,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S23" t="n">
+        <v>9.472041103692202</v>
+      </c>
+      <c r="T23" t="n">
+        <v>19.62893696133423</v>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1779,9 +1854,6 @@
       <c r="L24" t="n">
         <v>0.00052019</v>
       </c>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
       <c r="P24" t="n">
         <v>19.252</v>
       </c>
@@ -1795,6 +1867,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S24" t="n">
+        <v>11.82407529449587</v>
+      </c>
+      <c r="T24" t="n">
+        <v>29.15207134664004</v>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1835,9 +1913,6 @@
       <c r="L25" t="n">
         <v>0.00015363</v>
       </c>
-      <c r="M25" t="inlineStr"/>
-      <c r="N25" t="inlineStr"/>
-      <c r="O25" t="inlineStr"/>
       <c r="P25" t="n">
         <v>18.982</v>
       </c>
@@ -1851,6 +1926,12 @@
           <t>01/22/2026</t>
         </is>
       </c>
+      <c r="S25" t="n">
+        <v>13.24478446452019</v>
+      </c>
+      <c r="T25" t="n">
+        <v>19.97382929730345</v>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1891,9 +1972,6 @@
       <c r="L26" t="n">
         <v>0.00026543</v>
       </c>
-      <c r="M26" t="inlineStr"/>
-      <c r="N26" t="inlineStr"/>
-      <c r="O26" t="inlineStr"/>
       <c r="P26" t="n">
         <v>19.246</v>
       </c>
@@ -1907,7 +1985,14 @@
           <t>01/22/2026</t>
         </is>
       </c>
-    </row>
+      <c r="S26" t="n">
+        <v>11.43486810097261</v>
+      </c>
+      <c r="T26" t="n">
+        <v>94.81279528228055</v>
+      </c>
+    </row>
+    <row r="27"/>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
